--- a/tame_output/ON/bt/strategyON_20240901.xlsx
+++ b/tame_output/ON/bt/strategyON_20240901.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>46.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.7%</t>
+          <t>124.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-48.1%</t>
+          <t>-47.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.8%</t>
+          <t>422.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-688.8%</t>
+          <t>-688.6%</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-167.1%</t>
+          <t>-167.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.3%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>590.1%</t>
+          <t>589.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-309.0%</t>
+          <t>-308.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-164.2%</t>
+          <t>-161.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
     </row>
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.545291201695857</v>
+        <v>-4.498970438025959</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.928238378880493</v>
+        <v>1.946766684348452</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9035776166882092</v>
+        <v>0.9498983803581084</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.288857853885509</v>
+        <v>4.316650312087448</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.533237074782894</v>
+        <v>-4.486916311112996</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.926746597547116</v>
+        <v>1.945274903015076</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9156317436011721</v>
+        <v>0.9619525072710712</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.289776897934725</v>
+        <v>4.317569356136664</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.574392194351115</v>
+        <v>-4.528071430681217</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.912165179903963</v>
+        <v>1.930693485371923</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8744766240329511</v>
+        <v>0.9207973877028502</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.266964456377927</v>
+        <v>4.294756914579867</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.471511604822522</v>
+        <v>-4.425190841152624</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.966168441593283</v>
+        <v>1.984696747061243</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.977357213561544</v>
+        <v>1.023677977231443</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.341543835972966</v>
+        <v>4.369336294174905</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.703111997992023</v>
+        <v>-4.656791234322124</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.893730954499077</v>
+        <v>1.912259259967036</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.977357213561544</v>
+        <v>1.023677977231443</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.36174650614656</v>
+        <v>4.3895389643485</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.721184506283635</v>
+        <v>-4.674863742613736</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.886501951182432</v>
+        <v>1.905030256650392</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.977357213561544</v>
+        <v>1.023677977231443</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.36174650614656</v>
+        <v>4.3895389643485</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.896291338860079</v>
+        <v>-4.849970575190181</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.776711131745321</v>
+        <v>1.79523943721328</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.977357213561544</v>
+        <v>1.023677977231443</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.321998419740027</v>
+        <v>4.349790877941966</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.865005318319624</v>
+        <v>-4.818684554649725</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.796248158958443</v>
+        <v>1.814776464426403</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.008643234101999</v>
+        <v>1.054963997771898</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.34779265106124</v>
+        <v>4.375585109263179</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.71197992620634</v>
+        <v>-4.665659162536441</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.956629315376661</v>
+        <v>1.975157620844621</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.161668626215283</v>
+        <v>1.207989389885182</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.538778885902115</v>
+        <v>4.566571344104054</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.74028724007961</v>
+        <v>-4.693966476409711</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.132772614735646</v>
+        <v>2.151300920203605</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.161668626215283</v>
+        <v>1.207989389885182</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.726245110810407</v>
+        <v>4.754037569012346</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.906880465193132</v>
+        <v>-4.860559701523234</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.035538276044319</v>
+        <v>2.054066581512278</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9950754011017608</v>
+        <v>1.04139616477166</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.595692127096376</v>
+        <v>4.623484585298315</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.733816085810832</v>
+        <v>-4.687495322140934</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.108440430458956</v>
+        <v>2.126968735926916</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9950754011017608</v>
+        <v>1.04139616477166</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.599368529758094</v>
+        <v>4.627160987960033</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.704570105355136</v>
+        <v>-4.658249341685237</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.11775687776473</v>
+        <v>2.136285183232689</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9950754011017608</v>
+        <v>1.04139616477166</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.596986584881589</v>
+        <v>4.624779043083528</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.811495653232987</v>
+        <v>-4.765174889563088</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.072279897771225</v>
+        <v>2.090808203239185</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8881498532239095</v>
+        <v>0.9344706168938085</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.530124495312513</v>
+        <v>4.557916953514452</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.956514211740235</v>
+        <v>-4.910193448070337</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.015701276511559</v>
+        <v>2.034229581979519</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.743131294716661</v>
+        <v>0.78945205838656</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.444542162351398</v>
+        <v>4.472334620553338</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.074855977524953</v>
+        <v>-5.028535213855054</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.068295809455426</v>
+        <v>2.086824114923385</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.753817333279551</v>
+        <v>0.80013809694945</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.550885024746885</v>
+        <v>4.578677482948824</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.126266399845661</v>
+        <v>-5.079945636175762</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.045517337653081</v>
+        <v>2.064045643121041</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.753817333279551</v>
+        <v>0.80013809694945</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.548670721872823</v>
+        <v>4.576463180074763</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.205685851053413</v>
+        <v>-5.159365087383514</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.01365268524427</v>
+        <v>2.032180990712229</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.753817333279551</v>
+        <v>0.80013809694945</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.548573849947113</v>
+        <v>4.576366308149052</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.30114884897063</v>
+        <v>-5.254828085300732</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.975461379635426</v>
+        <v>1.993989685103386</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.753817333279551</v>
+        <v>0.80013809694945</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.548567743505156</v>
+        <v>4.576360201707096</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.341168847014414</v>
+        <v>-5.294848083344515</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.957549776980524</v>
+        <v>1.976078082448483</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7137973352357672</v>
+        <v>0.7601180989056662</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.522652141241497</v>
+        <v>4.550444599443436</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.396538009146608</v>
+        <v>-5.350217245476709</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.941135929875373</v>
+        <v>1.959664235343332</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7137973352357672</v>
+        <v>0.7601180989056662</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.528385958989223</v>
+        <v>4.556178417191163</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.441975788977435</v>
+        <v>-5.395655025307536</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.922499181285975</v>
+        <v>1.941027486753934</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6709523445576075</v>
+        <v>0.7172731082275066</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.502217327925261</v>
+        <v>4.5300097861272</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.35875033212977</v>
+        <v>-5.312429568459872</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.97566375687536</v>
+        <v>1.994192062343319</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6709523445576075</v>
+        <v>0.7172731082275066</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.52209172077558</v>
+        <v>4.54988417897752</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.182460107524463</v>
+        <v>-5.136139343854564</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.029880547242211</v>
+        <v>2.04840885271017</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6709523445576075</v>
+        <v>0.7172731082275066</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.505792421300308</v>
+        <v>4.533584879502247</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.999248444391368</v>
+        <v>-4.952927680721469</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.105596161959494</v>
+        <v>2.124124467427453</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6709523445576075</v>
+        <v>0.7172731082275066</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.508223370764354</v>
+        <v>4.536015828966293</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.927526997377517</v>
+        <v>-4.881206233707618</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.100075926612924</v>
+        <v>2.118604232080883</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7426737915714582</v>
+        <v>0.7889945552413572</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.517047424820553</v>
+        <v>4.544839883022492</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.056905780017295</v>
+        <v>-5.010585016347396</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.995240159478184</v>
+        <v>2.013768464946144</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7005720188642548</v>
+        <v>0.7468927825341538</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.438702107117402</v>
+        <v>4.466494565319342</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.089922075928039</v>
+        <v>-5.043601312258141</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.167231845999242</v>
+        <v>2.185760151467201</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6311346421975033</v>
+        <v>0.6774554058674023</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.582237886002707</v>
+        <v>4.610030344204646</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.078394440278431</v>
+        <v>-5.032073676608532</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.163764126087334</v>
+        <v>2.182292431555294</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6901353003988657</v>
+        <v>0.7364560640687647</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.609559506751774</v>
+        <v>4.637351964953713</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.1757359416208</v>
+        <v>-5.129415177950901</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.128495638072176</v>
+        <v>2.147023943540135</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6457151182333773</v>
+        <v>0.6920358819032764</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.586575509974269</v>
+        <v>4.614367968176209</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.808270274865567</v>
+        <v>3.749653658613644</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.272352755602648</v>
+        <v>-5.269841426439565</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.091099994672275</v>
+        <v>2.092104526337507</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5982557784122913</v>
+        <v>0.6278075708791069</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.559350988274455</v>
+        <v>4.577082063754546</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240901.xlsx
+++ b/tame_output/ON/bt/strategyON_20240901.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.8%</t>
+          <t>124.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>-44.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.5%</t>
+          <t>-49.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.7%</t>
+          <t>422.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-688.6%</t>
+          <t>-683.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-167.0%</t>
+          <t>-164.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>589.8%</t>
+          <t>589.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-161.2%</t>
+          <t>-159.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>83.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>13.0%</t>
         </is>
       </c>
     </row>
@@ -49230,16 +49230,16 @@
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.269841426439565</v>
+        <v>-5.215271207290868</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.092104526337507</v>
+        <v>2.113932613996986</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6278075708791069</v>
+        <v>0.6496598126771413</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.577082063754546</v>
+        <v>4.590193408833366</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240901.xlsx
+++ b/tame_output/ON/bt/strategyON_20240901.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>54.0%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-79.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-44.3%</t>
+          <t>-42.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-49.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.8%</t>
+          <t>423.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-683.1%</t>
+          <t>-680.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-164.8%</t>
+          <t>-163.6%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>589.5%</t>
+          <t>590.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-308.2%</t>
+          <t>-308.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-159.0%</t>
+          <t>-158.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>83.2%</t>
+          <t>83.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.4%</t>
         </is>
       </c>
     </row>
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.498970438025959</v>
+        <v>-4.545291201695857</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.946766684348452</v>
+        <v>1.928238378880493</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9498983803581084</v>
+        <v>0.9035776166882092</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.316650312087448</v>
+        <v>4.288857853885509</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.486916311112996</v>
+        <v>-4.533237074782894</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.945274903015076</v>
+        <v>1.926746597547116</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9619525072710712</v>
+        <v>0.9156317436011721</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.317569356136664</v>
+        <v>4.289776897934725</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.528071430681217</v>
+        <v>-4.574392194351115</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.930693485371923</v>
+        <v>1.912165179903963</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9207973877028502</v>
+        <v>0.8744766240329511</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.294756914579867</v>
+        <v>4.266964456377927</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.425190841152624</v>
+        <v>-4.471511604822522</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.984696747061243</v>
+        <v>1.966168441593283</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.023677977231443</v>
+        <v>0.977357213561544</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.369336294174905</v>
+        <v>4.341543835972966</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.656791234322124</v>
+        <v>-4.703111997992023</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.912259259967036</v>
+        <v>1.893730954499077</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.023677977231443</v>
+        <v>0.977357213561544</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.3895389643485</v>
+        <v>4.36174650614656</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.674863742613736</v>
+        <v>-4.721184506283635</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.905030256650392</v>
+        <v>1.886501951182432</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.023677977231443</v>
+        <v>0.977357213561544</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.3895389643485</v>
+        <v>4.36174650614656</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.849970575190181</v>
+        <v>-4.896291338860079</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.79523943721328</v>
+        <v>1.776711131745321</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.023677977231443</v>
+        <v>0.977357213561544</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.349790877941966</v>
+        <v>4.321998419740027</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.818684554649725</v>
+        <v>-4.865005318319624</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.814776464426403</v>
+        <v>1.796248158958443</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.054963997771898</v>
+        <v>1.008643234101999</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.375585109263179</v>
+        <v>4.34779265106124</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.665659162536441</v>
+        <v>-4.71197992620634</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.975157620844621</v>
+        <v>1.956629315376661</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.207989389885182</v>
+        <v>1.161668626215283</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.566571344104054</v>
+        <v>4.538778885902115</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.693966476409711</v>
+        <v>-4.74028724007961</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.151300920203605</v>
+        <v>2.132772614735646</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.207989389885182</v>
+        <v>1.161668626215283</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.754037569012346</v>
+        <v>4.726245110810407</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.860559701523234</v>
+        <v>-4.906880465193132</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.054066581512278</v>
+        <v>2.035538276044319</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.04139616477166</v>
+        <v>0.9950754011017608</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.623484585298315</v>
+        <v>4.595692127096376</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.687495322140934</v>
+        <v>-4.733816085810832</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.126968735926916</v>
+        <v>2.108440430458956</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.04139616477166</v>
+        <v>0.9950754011017608</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.627160987960033</v>
+        <v>4.599368529758094</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.658249341685237</v>
+        <v>-4.704570105355136</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.136285183232689</v>
+        <v>2.11775687776473</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.04139616477166</v>
+        <v>0.9950754011017608</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.624779043083528</v>
+        <v>4.596986584881589</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.765174889563088</v>
+        <v>-4.811495653232987</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.090808203239185</v>
+        <v>2.072279897771225</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9344706168938085</v>
+        <v>0.8881498532239095</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.557916953514452</v>
+        <v>4.530124495312513</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.910193448070337</v>
+        <v>-4.956514211740235</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.034229581979519</v>
+        <v>2.015701276511559</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.78945205838656</v>
+        <v>0.743131294716661</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.472334620553338</v>
+        <v>4.444542162351398</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.028535213855054</v>
+        <v>-5.074855977524953</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.086824114923385</v>
+        <v>2.068295809455426</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.80013809694945</v>
+        <v>0.753817333279551</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.578677482948824</v>
+        <v>4.550885024746885</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.079945636175762</v>
+        <v>-5.126266399845661</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.064045643121041</v>
+        <v>2.045517337653081</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.80013809694945</v>
+        <v>0.753817333279551</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.576463180074763</v>
+        <v>4.548670721872823</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.159365087383514</v>
+        <v>-5.205685851053413</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.032180990712229</v>
+        <v>2.01365268524427</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.80013809694945</v>
+        <v>0.753817333279551</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.576366308149052</v>
+        <v>4.548573849947113</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.254828085300732</v>
+        <v>-5.30114884897063</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.993989685103386</v>
+        <v>1.975461379635426</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.80013809694945</v>
+        <v>0.753817333279551</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.576360201707096</v>
+        <v>4.548567743505156</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.294848083344515</v>
+        <v>-5.341168847014414</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.976078082448483</v>
+        <v>1.957549776980524</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7601180989056662</v>
+        <v>0.7137973352357672</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.550444599443436</v>
+        <v>4.522652141241497</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.350217245476709</v>
+        <v>-5.396538009146608</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.959664235343332</v>
+        <v>1.941135929875373</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7601180989056662</v>
+        <v>0.7137973352357672</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.556178417191163</v>
+        <v>4.528385958989223</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.395655025307536</v>
+        <v>-5.364211251440367</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.941027486753934</v>
+        <v>1.953604996300802</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.7172731082275066</v>
+        <v>0.7235180215551757</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.5300097861272</v>
+        <v>4.533756734123802</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.312429568459872</v>
+        <v>-5.280985794592703</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.994192062343319</v>
+        <v>2.006769571890187</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.7172731082275066</v>
+        <v>0.7235180215551757</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.54988417897752</v>
+        <v>4.553631126974121</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.136139343854564</v>
+        <v>-5.104695569987395</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.04840885271017</v>
+        <v>2.060986362257037</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.7172731082275066</v>
+        <v>0.7235180215551757</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.533584879502247</v>
+        <v>4.537331827498848</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.952927680721469</v>
+        <v>-4.9214839068543</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.124124467427453</v>
+        <v>2.136701976974321</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.7172731082275066</v>
+        <v>0.7235180215551757</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.536015828966293</v>
+        <v>4.539762776962894</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.881206233707618</v>
+        <v>-4.849762459840449</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.118604232080883</v>
+        <v>2.131181741627751</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7889945552413572</v>
+        <v>0.7952394685690264</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.544839883022492</v>
+        <v>4.548586831019094</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.010585016347396</v>
+        <v>-4.979141242480227</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.013768464946144</v>
+        <v>2.026345974493011</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7468927825341538</v>
+        <v>0.753137695861823</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.466494565319342</v>
+        <v>4.470241513315943</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.043601312258141</v>
+        <v>-5.012157538390972</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.185760151467201</v>
+        <v>2.198337661014069</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6774554058674023</v>
+        <v>0.6837003191950715</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.610030344204646</v>
+        <v>4.613777292201248</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.032073676608532</v>
+        <v>-5.000629902741363</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.182292431555294</v>
+        <v>2.194869941102161</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7364560640687647</v>
+        <v>0.7427009773964339</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.637351964953713</v>
+        <v>4.641098912950315</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.129415177950901</v>
+        <v>-5.097971404083732</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.147023943540135</v>
+        <v>2.159601453087002</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6920358819032764</v>
+        <v>0.6982807952309456</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.614367968176209</v>
+        <v>4.61811491617281</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.749653658613644</v>
+        <v>3.820527329792454</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.215271207290868</v>
+        <v>-5.183827433423699</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.113932613996986</v>
+        <v>2.126510123543854</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6496598126771413</v>
+        <v>0.6559047260048105</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.590193408833366</v>
+        <v>4.593940356829967</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240901.xlsx
+++ b/tame_output/ON/bt/strategyON_20240901.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>108.4%</t>
+          <t>114.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.3%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.7%</t>
+          <t>124.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-42.3%</t>
+          <t>-41.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-49.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.8%</t>
+          <t>422.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-680.0%</t>
+          <t>-683.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-163.6%</t>
+          <t>-164.8%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>590.1%</t>
+          <t>589.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-308.3%</t>
+          <t>-308.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-158.4%</t>
+          <t>-159.0%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>83.4%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>-20.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2073"/>
+  <dimension ref="A1:G2074"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.545291201695857</v>
+        <v>-4.498970438025959</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.928238378880493</v>
+        <v>1.946766684348452</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9035776166882092</v>
+        <v>0.9498983803581084</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.288857853885509</v>
+        <v>4.316650312087448</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.533237074782894</v>
+        <v>-4.486916311112996</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.926746597547116</v>
+        <v>1.945274903015076</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9156317436011721</v>
+        <v>0.9619525072710712</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.289776897934725</v>
+        <v>4.317569356136664</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.574392194351115</v>
+        <v>-4.528071430681217</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.912165179903963</v>
+        <v>1.930693485371923</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8744766240329511</v>
+        <v>0.9207973877028502</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.266964456377927</v>
+        <v>4.294756914579867</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.471511604822522</v>
+        <v>-4.425190841152624</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.966168441593283</v>
+        <v>1.984696747061243</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.977357213561544</v>
+        <v>1.023677977231443</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.341543835972966</v>
+        <v>4.369336294174905</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.703111997992023</v>
+        <v>-4.656791234322124</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.893730954499077</v>
+        <v>1.912259259967036</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.977357213561544</v>
+        <v>1.023677977231443</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.36174650614656</v>
+        <v>4.3895389643485</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.721184506283635</v>
+        <v>-4.674863742613736</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.886501951182432</v>
+        <v>1.905030256650392</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.977357213561544</v>
+        <v>1.023677977231443</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.36174650614656</v>
+        <v>4.3895389643485</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.896291338860079</v>
+        <v>-4.849970575190181</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.776711131745321</v>
+        <v>1.79523943721328</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.977357213561544</v>
+        <v>1.023677977231443</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.321998419740027</v>
+        <v>4.349790877941966</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.865005318319624</v>
+        <v>-4.818684554649725</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.796248158958443</v>
+        <v>1.814776464426403</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.008643234101999</v>
+        <v>1.054963997771898</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.34779265106124</v>
+        <v>4.375585109263179</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.71197992620634</v>
+        <v>-4.665659162536441</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.956629315376661</v>
+        <v>1.975157620844621</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.161668626215283</v>
+        <v>1.207989389885182</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.538778885902115</v>
+        <v>4.566571344104054</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.74028724007961</v>
+        <v>-4.693966476409711</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.132772614735646</v>
+        <v>2.151300920203605</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.161668626215283</v>
+        <v>1.207989389885182</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.726245110810407</v>
+        <v>4.754037569012346</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.906880465193132</v>
+        <v>-4.860559701523234</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.035538276044319</v>
+        <v>2.054066581512278</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9950754011017608</v>
+        <v>1.04139616477166</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.595692127096376</v>
+        <v>4.623484585298315</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.733816085810832</v>
+        <v>-4.687495322140934</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.108440430458956</v>
+        <v>2.126968735926916</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9950754011017608</v>
+        <v>1.04139616477166</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.599368529758094</v>
+        <v>4.627160987960033</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.704570105355136</v>
+        <v>-4.658249341685237</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.11775687776473</v>
+        <v>2.136285183232689</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9950754011017608</v>
+        <v>1.04139616477166</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.596986584881589</v>
+        <v>4.624779043083528</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.811495653232987</v>
+        <v>-4.765174889563088</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.072279897771225</v>
+        <v>2.090808203239185</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8881498532239095</v>
+        <v>0.9344706168938085</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.530124495312513</v>
+        <v>4.557916953514452</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.956514211740235</v>
+        <v>-4.910193448070337</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.015701276511559</v>
+        <v>2.034229581979519</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.743131294716661</v>
+        <v>0.78945205838656</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.444542162351398</v>
+        <v>4.472334620553338</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.074855977524953</v>
+        <v>-5.028535213855054</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.068295809455426</v>
+        <v>2.086824114923385</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.753817333279551</v>
+        <v>0.80013809694945</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.550885024746885</v>
+        <v>4.578677482948824</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.126266399845661</v>
+        <v>-5.079945636175762</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.045517337653081</v>
+        <v>2.064045643121041</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.753817333279551</v>
+        <v>0.80013809694945</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.548670721872823</v>
+        <v>4.576463180074763</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.205685851053413</v>
+        <v>-5.159365087383514</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.01365268524427</v>
+        <v>2.032180990712229</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.753817333279551</v>
+        <v>0.80013809694945</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.548573849947113</v>
+        <v>4.576366308149052</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.30114884897063</v>
+        <v>-5.254828085300732</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.975461379635426</v>
+        <v>1.993989685103386</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.753817333279551</v>
+        <v>0.80013809694945</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.548567743505156</v>
+        <v>4.576360201707096</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.341168847014414</v>
+        <v>-5.294848083344515</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.957549776980524</v>
+        <v>1.976078082448483</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7137973352357672</v>
+        <v>0.7601180989056662</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.522652141241497</v>
+        <v>4.550444599443436</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.396538009146608</v>
+        <v>-5.350217245476709</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.941135929875373</v>
+        <v>1.959664235343332</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7137973352357672</v>
+        <v>0.7601180989056662</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.528385958989223</v>
+        <v>4.556178417191163</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.364211251440367</v>
+        <v>-5.395655025307536</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.953604996300802</v>
+        <v>1.941027486753934</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.7235180215551757</v>
+        <v>0.7172731082275066</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.533756734123802</v>
+        <v>4.5300097861272</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.280985794592703</v>
+        <v>-5.312429568459872</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.006769571890187</v>
+        <v>1.994192062343319</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.7235180215551757</v>
+        <v>0.7172731082275066</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.553631126974121</v>
+        <v>4.54988417897752</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.104695569987395</v>
+        <v>-5.136139343854564</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.060986362257037</v>
+        <v>2.04840885271017</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.7235180215551757</v>
+        <v>0.7172731082275066</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.537331827498848</v>
+        <v>4.533584879502247</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.9214839068543</v>
+        <v>-4.952927680721469</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.136701976974321</v>
+        <v>2.124124467427453</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.7235180215551757</v>
+        <v>0.7172731082275066</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.539762776962894</v>
+        <v>4.536015828966293</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.849762459840449</v>
+        <v>-4.881206233707618</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.131181741627751</v>
+        <v>2.118604232080883</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7952394685690264</v>
+        <v>0.7889945552413572</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.548586831019094</v>
+        <v>4.544839883022492</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.979141242480227</v>
+        <v>-5.010585016347396</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.026345974493011</v>
+        <v>2.013768464946144</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.753137695861823</v>
+        <v>0.7468927825341538</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.470241513315943</v>
+        <v>4.466494565319342</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.012157538390972</v>
+        <v>-5.043601312258141</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.198337661014069</v>
+        <v>2.185760151467201</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6837003191950715</v>
+        <v>0.6774554058674023</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.613777292201248</v>
+        <v>4.610030344204646</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.000629902741363</v>
+        <v>-5.032073676608532</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.194869941102161</v>
+        <v>2.182292431555294</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7427009773964339</v>
+        <v>0.7364560640687647</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.641098912950315</v>
+        <v>4.637351964953713</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.097971404083732</v>
+        <v>-5.129415177950901</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.159601453087002</v>
+        <v>2.147023943540135</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6982807952309456</v>
+        <v>0.6920358819032764</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.61811491617281</v>
+        <v>4.614367968176209</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,45 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.820527329792454</v>
+        <v>3.705221264710415</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.183827433423699</v>
+        <v>-5.215271207290868</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.126510123543854</v>
+        <v>2.113932613996986</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6559047260048105</v>
+        <v>0.6496598126771413</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.593940356829967</v>
+        <v>4.590193408833366</v>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" s="2" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B2074" t="n">
+        <v>3.750191030214298</v>
+      </c>
+      <c r="C2074" t="n">
+        <v>4.258563909303484</v>
+      </c>
+      <c r="D2074" t="n">
+        <v>-5.215271207290868</v>
+      </c>
+      <c r="E2074" t="n">
+        <v>2.113932613996986</v>
+      </c>
+      <c r="F2074" t="n">
+        <v>0.6496598126771413</v>
+      </c>
+      <c r="G2074" t="n">
+        <v>4.251627706289852</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240901.xlsx
+++ b/tame_output/ON/bt/strategyON_20240901.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>114.2%</t>
+          <t>116.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-41.9%</t>
+          <t>-38.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-49.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.8%</t>
+          <t>422.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-683.1%</t>
+          <t>-676.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-164.8%</t>
+          <t>-162.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>589.5%</t>
+          <t>589.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-308.2%</t>
+          <t>-307.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-159.0%</t>
+          <t>-155.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-18.2%</t>
         </is>
       </c>
     </row>
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.498970438025959</v>
+        <v>-4.545291201695857</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.946766684348452</v>
+        <v>1.928238378880493</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9498983803581084</v>
+        <v>0.9035776166882092</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.316650312087448</v>
+        <v>4.288857853885509</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.486916311112996</v>
+        <v>-4.502929580074317</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.945274903015076</v>
+        <v>1.938869595430547</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9619525072710712</v>
+        <v>0.9459392383097491</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.317569356136664</v>
+        <v>4.307961394759871</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.528071430681217</v>
+        <v>-4.544084699642538</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.930693485371923</v>
+        <v>1.924288177787394</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9207973877028502</v>
+        <v>0.9047841187415282</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.294756914579867</v>
+        <v>4.285148953203074</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.425190841152624</v>
+        <v>-4.441204110113945</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.984696747061243</v>
+        <v>1.978291439476714</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.023677977231443</v>
+        <v>1.007664708270121</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.369336294174905</v>
+        <v>4.359728332798112</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.656791234322124</v>
+        <v>-4.672804503283446</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.912259259967036</v>
+        <v>1.905853952382508</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.023677977231443</v>
+        <v>1.007664708270121</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.3895389643485</v>
+        <v>4.379931002971706</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.674863742613736</v>
+        <v>-4.690877011575058</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.905030256650392</v>
+        <v>1.898624949065863</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.023677977231443</v>
+        <v>1.007664708270121</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.3895389643485</v>
+        <v>4.379931002971706</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.849970575190181</v>
+        <v>-4.865983844151502</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.79523943721328</v>
+        <v>1.788834129628752</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.023677977231443</v>
+        <v>1.007664708270121</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.349790877941966</v>
+        <v>4.340182916565173</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.818684554649725</v>
+        <v>-4.834697823611047</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.814776464426403</v>
+        <v>1.808371156841874</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.054963997771898</v>
+        <v>1.038950728810577</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.375585109263179</v>
+        <v>4.365977147886387</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.665659162536441</v>
+        <v>-4.681672431497763</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.975157620844621</v>
+        <v>1.968752313260092</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.207989389885182</v>
+        <v>1.191976120923861</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.566571344104054</v>
+        <v>4.556963382727261</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.693966476409711</v>
+        <v>-4.709979745371033</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.151300920203605</v>
+        <v>2.144895612619076</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.207989389885182</v>
+        <v>1.191976120923861</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.754037569012346</v>
+        <v>4.744429607635553</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.860559701523234</v>
+        <v>-4.876572970484555</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.054066581512278</v>
+        <v>2.04766127392775</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.04139616477166</v>
+        <v>1.025382895810338</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.623484585298315</v>
+        <v>4.613876623921522</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.687495322140934</v>
+        <v>-4.703508591102255</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.126968735926916</v>
+        <v>2.120563428342387</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.04139616477166</v>
+        <v>1.025382895810338</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.627160987960033</v>
+        <v>4.61755302658324</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.658249341685237</v>
+        <v>-4.674262610646559</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.136285183232689</v>
+        <v>2.129879875648161</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.04139616477166</v>
+        <v>1.025382895810338</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.624779043083528</v>
+        <v>4.615171081706735</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.765174889563088</v>
+        <v>-4.78118815852441</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.090808203239185</v>
+        <v>2.084402895654656</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9344706168938085</v>
+        <v>0.9184573479324868</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.557916953514452</v>
+        <v>4.54830899213766</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.910193448070337</v>
+        <v>-4.926206717031659</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.034229581979519</v>
+        <v>2.02782427439499</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.78945205838656</v>
+        <v>0.7734387894252382</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.472334620553338</v>
+        <v>4.462726659176544</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.028535213855054</v>
+        <v>-5.044548482816376</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.086824114923385</v>
+        <v>2.080418807338857</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.80013809694945</v>
+        <v>0.7841248279881283</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.578677482948824</v>
+        <v>4.569069521572032</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.079945636175762</v>
+        <v>-5.095958905137084</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.064045643121041</v>
+        <v>2.057640335536512</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.80013809694945</v>
+        <v>0.7841248279881283</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.576463180074763</v>
+        <v>4.56685521869797</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.159365087383514</v>
+        <v>-5.175378356344836</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.032180990712229</v>
+        <v>2.025775683127701</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.80013809694945</v>
+        <v>0.7841248279881283</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.576366308149052</v>
+        <v>4.56675834677226</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.254828085300732</v>
+        <v>-5.270841354262053</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.993989685103386</v>
+        <v>1.987584377518857</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.80013809694945</v>
+        <v>0.7841248279881283</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.576360201707096</v>
+        <v>4.566752240330303</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.294848083344515</v>
+        <v>-5.310861352305837</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.976078082448483</v>
+        <v>1.969672774863954</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7601180989056662</v>
+        <v>0.7441048299443445</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.550444599443436</v>
+        <v>4.540836638066644</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.350217245476709</v>
+        <v>-5.366230514438031</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.959664235343332</v>
+        <v>1.953258927758803</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7601180989056662</v>
+        <v>0.7441048299443445</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.556178417191163</v>
+        <v>4.54657045581437</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.395655025307536</v>
+        <v>-5.33390375673179</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.941027486753934</v>
+        <v>1.965727994184232</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.7172731082275066</v>
+        <v>0.753825516263753</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.5300097861272</v>
+        <v>4.551941230948948</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.312429568459872</v>
+        <v>-5.250678299884126</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.994192062343319</v>
+        <v>2.018892569773617</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.7172731082275066</v>
+        <v>0.753825516263753</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.54988417897752</v>
+        <v>4.571815623799267</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.136139343854564</v>
+        <v>-5.074388075278819</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.04840885271017</v>
+        <v>2.073109360140468</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.7172731082275066</v>
+        <v>0.753825516263753</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.533584879502247</v>
+        <v>4.555516324323995</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.952927680721469</v>
+        <v>-4.891176412145724</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.124124467427453</v>
+        <v>2.148824974857752</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.7172731082275066</v>
+        <v>0.753825516263753</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.536015828966293</v>
+        <v>4.557947273788041</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.881206233707618</v>
+        <v>-4.819454965131873</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.118604232080883</v>
+        <v>2.143304739511182</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7889945552413572</v>
+        <v>0.8255469632776037</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.544839883022492</v>
+        <v>4.56677132784424</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.010585016347396</v>
+        <v>-4.94883374777165</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.013768464946144</v>
+        <v>2.038468972376442</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7468927825341538</v>
+        <v>0.7834451905704003</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.466494565319342</v>
+        <v>4.48842601014109</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.043601312258141</v>
+        <v>-4.981850043682395</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.185760151467201</v>
+        <v>2.2104606588975</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6774554058674023</v>
+        <v>0.7140078139036488</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.610030344204646</v>
+        <v>4.631961789026395</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.032073676608532</v>
+        <v>-4.970322408032787</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.182292431555294</v>
+        <v>2.206992938985592</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7364560640687647</v>
+        <v>0.7730084721050112</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.637351964953713</v>
+        <v>4.659283409775461</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.129415177950901</v>
+        <v>-5.067663909375155</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.147023943540135</v>
+        <v>2.171724450970433</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6920358819032764</v>
+        <v>0.7285882899395228</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.614367968176209</v>
+        <v>4.636299412997957</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.215271207290868</v>
+        <v>-5.153519938715122</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.113932613996986</v>
+        <v>2.138633121427285</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6496598126771413</v>
+        <v>0.6862122207133878</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.590193408833366</v>
+        <v>4.612124853655113</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.750191030214298</v>
+        <v>3.756040062606192</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.258563909303484</v>
+        <v>4.285082346681342</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.215271207290868</v>
+        <v>-5.153519938715122</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.113932613996986</v>
+        <v>2.138633121427285</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6496598126771413</v>
+        <v>0.6862122207133878</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.251627706289852</v>
+        <v>4.27814614366771</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240901.xlsx
+++ b/tame_output/ON/bt/strategyON_20240901.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-38.2%</t>
+          <t>-43.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.1%</t>
+          <t>-49.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.9%</t>
+          <t>422.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-676.9%</t>
+          <t>-686.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-162.4%</t>
+          <t>-166.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>589.8%</t>
+          <t>590.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-307.7%</t>
+          <t>-308.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-155.4%</t>
+          <t>-162.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-23.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.502929580074317</v>
+        <v>-4.517659840186394</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.938869595430547</v>
+        <v>1.932977491385716</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9459392383097491</v>
+        <v>0.9312089781976722</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.307961394759871</v>
+        <v>4.299123238692625</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.544084699642538</v>
+        <v>-4.558814959754615</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.924288177787394</v>
+        <v>1.918396073742564</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9047841187415282</v>
+        <v>0.8900538586294513</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.285148953203074</v>
+        <v>4.276310797135828</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.441204110113945</v>
+        <v>-4.455934370226022</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.978291439476714</v>
+        <v>1.972399335431883</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.007664708270121</v>
+        <v>0.9929344481580442</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.359728332798112</v>
+        <v>4.350890176730866</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.672804503283446</v>
+        <v>-4.687534763395523</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.905853952382508</v>
+        <v>1.899961848337677</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.007664708270121</v>
+        <v>0.9929344481580442</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.379931002971706</v>
+        <v>4.37109284690446</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.690877011575058</v>
+        <v>-4.705607271687135</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.898624949065863</v>
+        <v>1.892732845021032</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.007664708270121</v>
+        <v>0.9929344481580442</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.379931002971706</v>
+        <v>4.37109284690446</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.865983844151502</v>
+        <v>-4.88071410426358</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.788834129628752</v>
+        <v>1.782942025583921</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.007664708270121</v>
+        <v>0.9929344481580442</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.340182916565173</v>
+        <v>4.331344760497926</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.834697823611047</v>
+        <v>-4.849428083723125</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.808371156841874</v>
+        <v>1.802479052797043</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.038950728810577</v>
+        <v>1.0242204686985</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.365977147886387</v>
+        <v>4.35713899181914</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.681672431497763</v>
+        <v>-4.69640269160984</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.968752313260092</v>
+        <v>1.962860209215261</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.191976120923861</v>
+        <v>1.177245860811784</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.556963382727261</v>
+        <v>4.548125226660015</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.709979745371033</v>
+        <v>-4.724710005483111</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.144895612619076</v>
+        <v>2.139003508574245</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.191976120923861</v>
+        <v>1.177245860811784</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.744429607635553</v>
+        <v>4.735591451568308</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.876572970484555</v>
+        <v>-4.891303230596633</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.04766127392775</v>
+        <v>2.041769169882918</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.025382895810338</v>
+        <v>1.010652635698261</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.613876623921522</v>
+        <v>4.605038467854276</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.703508591102255</v>
+        <v>-4.718238851214333</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.120563428342387</v>
+        <v>2.114671324297556</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.025382895810338</v>
+        <v>1.010652635698261</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.61755302658324</v>
+        <v>4.608714870515993</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.674262610646559</v>
+        <v>-4.688992870758637</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.129879875648161</v>
+        <v>2.12398777160333</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.025382895810338</v>
+        <v>1.010652635698261</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.615171081706735</v>
+        <v>4.606332925639489</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.78118815852441</v>
+        <v>-4.795918418636488</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.084402895654656</v>
+        <v>2.078510791609824</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9184573479324868</v>
+        <v>0.9037270878204099</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.54830899213766</v>
+        <v>4.539470836070413</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.926206717031659</v>
+        <v>-4.940936977143736</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.02782427439499</v>
+        <v>2.021932170350159</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7734387894252382</v>
+        <v>0.7587085293131614</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.462726659176544</v>
+        <v>4.453888503109298</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.044548482816376</v>
+        <v>-5.059278742928454</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.080418807338857</v>
+        <v>2.074526703294025</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7841248279881283</v>
+        <v>0.7693945678760514</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.569069521572032</v>
+        <v>4.560231365504785</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.095958905137084</v>
+        <v>-5.110689165249162</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.057640335536512</v>
+        <v>2.051748231491681</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7841248279881283</v>
+        <v>0.7693945678760514</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.56685521869797</v>
+        <v>4.558017062630724</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.175378356344836</v>
+        <v>-5.190108616456913</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.025775683127701</v>
+        <v>2.01988357908287</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7841248279881283</v>
+        <v>0.7693945678760514</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.56675834677226</v>
+        <v>4.557920190705014</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.270841354262053</v>
+        <v>-5.285571614374131</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.987584377518857</v>
+        <v>1.981692273474026</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7841248279881283</v>
+        <v>0.7693945678760514</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.566752240330303</v>
+        <v>4.557914084263057</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.310861352305837</v>
+        <v>-5.325591612417915</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.969672774863954</v>
+        <v>1.963780670819123</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7441048299443445</v>
+        <v>0.7293745698322676</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.540836638066644</v>
+        <v>4.531998481999397</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.366230514438031</v>
+        <v>-5.380960774550108</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.953258927758803</v>
+        <v>1.947366823713972</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7441048299443445</v>
+        <v>0.7293745698322676</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.54657045581437</v>
+        <v>4.537732299747124</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.33390375673179</v>
+        <v>-5.426398554380936</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.965727994184232</v>
+        <v>1.928730075124574</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.753825516263753</v>
+        <v>0.6865295791541079</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.551941230948948</v>
+        <v>4.511563668683161</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.250678299884126</v>
+        <v>-5.343173097533271</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.018892569773617</v>
+        <v>1.981894650713959</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.753825516263753</v>
+        <v>0.6865295791541079</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.571815623799267</v>
+        <v>4.53143806153348</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.074388075278819</v>
+        <v>-5.166882872927964</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.073109360140468</v>
+        <v>2.03611144108081</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.753825516263753</v>
+        <v>0.6865295791541079</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.555516324323995</v>
+        <v>4.515138762058208</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.891176412145724</v>
+        <v>-4.983671209794869</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.148824974857752</v>
+        <v>2.111827055798094</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.753825516263753</v>
+        <v>0.6865295791541079</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.557947273788041</v>
+        <v>4.517569711522254</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.819454965131873</v>
+        <v>-4.911949762781018</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.143304739511182</v>
+        <v>2.106306820451524</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.8255469632776037</v>
+        <v>0.7582510261679586</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.56677132784424</v>
+        <v>4.526393765578453</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.94883374777165</v>
+        <v>-5.041328545420796</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.038468972376442</v>
+        <v>2.001471053316784</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7834451905704003</v>
+        <v>0.7161492534607552</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.48842601014109</v>
+        <v>4.448048447875303</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.981850043682395</v>
+        <v>-5.07434484133154</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.2104606588975</v>
+        <v>2.173462739837841</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.7140078139036488</v>
+        <v>0.6467118767940037</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.631961789026395</v>
+        <v>4.591584226760608</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.970322408032787</v>
+        <v>-5.062817205681932</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.206992938985592</v>
+        <v>2.169995019925934</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7730084721050112</v>
+        <v>0.7057125349953661</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.659283409775461</v>
+        <v>4.618905847509674</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.067663909375155</v>
+        <v>-5.1601587070243</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.171724450970433</v>
+        <v>2.134726531910775</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.7285882899395228</v>
+        <v>0.6612923528298777</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.636299412997957</v>
+        <v>4.59592185073217</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.153519938715122</v>
+        <v>-5.246014736364267</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.138633121427285</v>
+        <v>2.101635202367627</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6862122207133878</v>
+        <v>0.6189162836037427</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.612124853655113</v>
+        <v>4.571747291389327</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,13 +49253,13 @@
         <v>4.285082346681342</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.153519938715122</v>
+        <v>-5.246014736364267</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.138633121427285</v>
+        <v>2.101635202367627</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6862122207133878</v>
+        <v>0.6189162836037427</v>
       </c>
       <c r="G2074" t="n">
         <v>4.27814614366771</v>

--- a/tame_output/ON/bt/strategyON_20240901.xlsx
+++ b/tame_output/ON/bt/strategyON_20240901.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>76.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>116.9%</t>
+          <t>106.7%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-47.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-686.2%</t>
+          <t>-690.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-32.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-166.1%</t>
+          <t>-169.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>590.2%</t>
+          <t>590.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-162.1%</t>
+          <t>-162.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>81.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>8.9%</t>
         </is>
       </c>
     </row>
@@ -49250,19 +49250,19 @@
         <v>3.756040062606192</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.285082346681342</v>
+        <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.246014736364267</v>
+        <v>-5.288865690686579</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.101635202367627</v>
+        <v>2.066914022459204</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6189162836037427</v>
+        <v>0.6106660569491643</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.27814614366771</v>
+        <v>4.549216357217081</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240901.xlsx
+++ b/tame_output/ON/bt/strategyON_20240901.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-43.7%</t>
+          <t>-41.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.8%</t>
+          <t>422.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-690.5%</t>
+          <t>-685.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-169.5%</t>
+          <t>-167.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>590.3%</t>
+          <t>589.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-308.3%</t>
+          <t>-308.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-162.9%</t>
+          <t>-159.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-20.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
     </row>
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.517659840186394</v>
+        <v>-4.533237074782894</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.932977491385716</v>
+        <v>1.926746597547116</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9312089781976722</v>
+        <v>0.9156317436011721</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.299123238692625</v>
+        <v>4.289776897934725</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.558814959754615</v>
+        <v>-4.535035832450172</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.918396073742564</v>
+        <v>1.92790772466434</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8900538586294513</v>
+        <v>0.9138329859338936</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.276310797135828</v>
+        <v>4.290578273518493</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.455934370226022</v>
+        <v>-4.43215524292158</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.972399335431883</v>
+        <v>1.98191098635366</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9929344481580442</v>
+        <v>1.016713575462487</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.350890176730866</v>
+        <v>4.365157653113531</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.687534763395523</v>
+        <v>-4.66375563609108</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.899961848337677</v>
+        <v>1.909473499259454</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9929344481580442</v>
+        <v>1.016713575462487</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.37109284690446</v>
+        <v>4.385360323287125</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.705607271687135</v>
+        <v>-4.681828144382692</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.892732845021032</v>
+        <v>1.902244495942809</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9929344481580442</v>
+        <v>1.016713575462487</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.37109284690446</v>
+        <v>4.385360323287125</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.88071410426358</v>
+        <v>-4.856934976959137</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.782942025583921</v>
+        <v>1.792453676505698</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9929344481580442</v>
+        <v>1.016713575462487</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.331344760497926</v>
+        <v>4.345612236880593</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.849428083723125</v>
+        <v>-4.825648956418681</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.802479052797043</v>
+        <v>1.81199070371882</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.0242204686985</v>
+        <v>1.047999596002942</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.35713899181914</v>
+        <v>4.371406468201806</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.69640269160984</v>
+        <v>-4.672623564305397</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.962860209215261</v>
+        <v>1.972371860137038</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.177245860811784</v>
+        <v>1.201024988116226</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.548125226660015</v>
+        <v>4.56239270304268</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.724710005483111</v>
+        <v>-4.700930878178667</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.139003508574245</v>
+        <v>2.148515159496022</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.177245860811784</v>
+        <v>1.201024988116226</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.735591451568308</v>
+        <v>4.749858927950973</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.891303230596633</v>
+        <v>-4.867524103292189</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.041769169882918</v>
+        <v>2.051280820804696</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.010652635698261</v>
+        <v>1.034431763002704</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.605038467854276</v>
+        <v>4.619305944236941</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.718238851214333</v>
+        <v>-4.69445972390989</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.114671324297556</v>
+        <v>2.124182975219334</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.010652635698261</v>
+        <v>1.034431763002704</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.608714870515993</v>
+        <v>4.622982346898659</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.688992870758637</v>
+        <v>-4.665213743454193</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.12398777160333</v>
+        <v>2.133499422525107</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.010652635698261</v>
+        <v>1.034431763002704</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.606332925639489</v>
+        <v>4.620600402022154</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.795918418636488</v>
+        <v>-4.772139291332044</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.078510791609824</v>
+        <v>2.088022442531602</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9037270878204099</v>
+        <v>0.9275062151248522</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.539470836070413</v>
+        <v>4.553738312453079</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.940936977143736</v>
+        <v>-4.917157849839293</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.021932170350159</v>
+        <v>2.031443821271937</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7587085293131614</v>
+        <v>0.7824876566176037</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.453888503109298</v>
+        <v>4.468155979491963</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.059278742928454</v>
+        <v>-5.03549961562401</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.074526703294025</v>
+        <v>2.084038354215803</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7693945678760514</v>
+        <v>0.7931736951804937</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.560231365504785</v>
+        <v>4.574498841887451</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.110689165249162</v>
+        <v>-5.086910037944718</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.051748231491681</v>
+        <v>2.061259882413458</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7693945678760514</v>
+        <v>0.7931736951804937</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.558017062630724</v>
+        <v>4.572284539013389</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.190108616456913</v>
+        <v>-5.16632948915247</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.01988357908287</v>
+        <v>2.029395230004647</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7693945678760514</v>
+        <v>0.7931736951804937</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.557920190705014</v>
+        <v>4.572187667087679</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.285571614374131</v>
+        <v>-5.261792487069687</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.981692273474026</v>
+        <v>1.991203924395804</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7693945678760514</v>
+        <v>0.7931736951804937</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.557914084263057</v>
+        <v>4.572181560645722</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.325591612417915</v>
+        <v>-5.301812485113471</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.963780670819123</v>
+        <v>1.973292321740901</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7293745698322676</v>
+        <v>0.7531536971367099</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.531998481999397</v>
+        <v>4.546265958382063</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.380960774550108</v>
+        <v>-5.357181647245665</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.947366823713972</v>
+        <v>1.95687847463575</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7293745698322676</v>
+        <v>0.7531536971367099</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.537732299747124</v>
+        <v>4.551999776129789</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.426398554380936</v>
+        <v>-5.402619427076492</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.928730075124574</v>
+        <v>1.938241726046352</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6865295791541079</v>
+        <v>0.7103087064585503</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.511563668683161</v>
+        <v>4.525831145065826</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.343173097533271</v>
+        <v>-5.300708017188054</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.981894650713959</v>
+        <v>1.998880682852046</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6865295791541079</v>
+        <v>0.7103087064585503</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.53143806153348</v>
+        <v>4.545705537916145</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.166882872927964</v>
+        <v>-5.124417792582746</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.03611144108081</v>
+        <v>2.053097473218897</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6865295791541079</v>
+        <v>0.7103087064585503</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.515138762058208</v>
+        <v>4.529406238440873</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.983671209794869</v>
+        <v>-4.941206129449651</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.111827055798094</v>
+        <v>2.128813087936181</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6865295791541079</v>
+        <v>0.7103087064585503</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.517569711522254</v>
+        <v>4.531837187904919</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.911949762781018</v>
+        <v>-4.8694846824358</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.106306820451524</v>
+        <v>2.123292852589611</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7582510261679586</v>
+        <v>0.7820301534724009</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.526393765578453</v>
+        <v>4.540661241961119</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.041328545420796</v>
+        <v>-4.998863465075578</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.001471053316784</v>
+        <v>2.018457085454871</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7161492534607552</v>
+        <v>0.7399283807651975</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.448048447875303</v>
+        <v>4.462315924257968</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.07434484133154</v>
+        <v>-5.031879760986323</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.173462739837841</v>
+        <v>2.190448771975928</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6467118767940037</v>
+        <v>0.670491004098446</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.591584226760608</v>
+        <v>4.605851703143273</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.062817205681932</v>
+        <v>-5.020352125336714</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.169995019925934</v>
+        <v>2.186981052064021</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7057125349953661</v>
+        <v>0.7294916622998084</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.618905847509674</v>
+        <v>4.633173323892339</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.1601587070243</v>
+        <v>-5.117693626679083</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.134726531910775</v>
+        <v>2.151712564048862</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6612923528298777</v>
+        <v>0.6850714801343201</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.59592185073217</v>
+        <v>4.610189327114835</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.246014736364267</v>
+        <v>-5.20354965601905</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.101635202367627</v>
+        <v>2.118621234505714</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6189162836037427</v>
+        <v>0.642695410908185</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.571747291389327</v>
+        <v>4.586014767771992</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.756040062606192</v>
+        <v>3.74236452559339</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.288865690686579</v>
+        <v>-5.235413639967661</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.066914022459204</v>
+        <v>2.088294842746771</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6106660569491643</v>
+        <v>0.642695410908185</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.549216357217081</v>
+        <v>4.568433969592494</v>
       </c>
     </row>
   </sheetData>
